--- a/consent_forms/043_texas_telemedicine_consent_form--consent_forms.xlsx
+++ b/consent_forms/043_texas_telemedicine_consent_form--consent_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Medical Provider State</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Zip Code</t>
+          <t>Medical Provider Zip</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Medical Provider Phone</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Medical Provider Email</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
